--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:16</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>48.56</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>112.85</v>
+        <v>112.84</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>64.28</v>
@@ -535,7 +535,7 @@
         <v>13.56</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>47.67</v>
+        <v>47.66</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>34.1</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:43</t>
+    <t xml:space="preserve">2026-10-05 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,10 +493,10 @@
         <v>48.56</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>112.84</v>
+        <v>112.85</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>64.28</v>
+        <v>64.29</v>
       </c>
     </row>
     <row r="3">
@@ -535,10 +535,10 @@
         <v>13.56</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>47.66</v>
+        <v>47.67</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34.1</v>
+        <v>34.11</v>
       </c>
     </row>
   </sheetData>
